--- a/data/bidbuddy_conversations.xlsx
+++ b/data/bidbuddy_conversations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,16 @@
           <t>Sources</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Public IP</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Approximate Location</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -494,7 +504,46 @@
           <t>faq</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Siddharth Sahni</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>42f26f45-995e-43f6-9f82-39811c8ebe46</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>esim in etm</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes, e-SIM functionality can be implemented in ETIMs. The devices are highly configurable and can be customized as per project or authority requirements.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>faq</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/bidbuddy_conversations.xlsx
+++ b/data/bidbuddy_conversations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,9 +541,46 @@
           <t>faq</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:31:15+00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Siddharth Sahni</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>42f26f45-995e-43f6-9f82-39811c8ebe46</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>battery of etm</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ETIM devices typically provide a battery backup of 10-12 hours on a single charge, depending on usage. The charging time is approximately 1.5 to 2 hours for a full recharge.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>faq</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
